--- a/out/Attention-MambaAMT_repeat_5_000001.xlsx
+++ b/out/Attention-MambaAMT_repeat_5_000001.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.501156825476262</v>
+        <v>2.43186320216187</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.501156825476262</v>
+        <v>2.43186320216187</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.501156825476262</v>
+        <v>3.031863202161869</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.501156825476262</v>
+        <v>3.031863202161869</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.501156825476262</v>
+        <v>3.031863202161869</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.501156825476262</v>
+        <v>3.031863202161869</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.417459022789986</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.417459022789986</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.501156825476262</v>
+        <v>3.031863202161869</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.501156825476262</v>
+        <v>3.031863202161869</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.501156825476262</v>
+        <v>3.031863202161869</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.501156825476262</v>
+        <v>3.031863202161869</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.501156825476262</v>
+        <v>3.031863202161869</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.501156825476262</v>
+        <v>3.031863202161869</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.501156825476262</v>
+        <v>3.031863202161869</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.501156825476262</v>
+        <v>3.031863202161869</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.501156825476262</v>
+        <v>3.031863202161869</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.501156825476262</v>
+        <v>2.43186320216187</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.501156825476262</v>
+        <v>2.43186320216187</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.501156825476262</v>
+        <v>2.43186320216187</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.501156825476262</v>
+        <v>2.43186320216187</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.501156825476262</v>
+        <v>2.43186320216187</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.501156825476262</v>
+        <v>2.43186320216187</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.931760215741336</v>
+        <v>2.43186320216187</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.931760215741336</v>
+        <v>3.031863202161869</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.9011568254762614</v>
+        <v>3.031863202161869</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.417459022789986</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.417459022789986</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002577772592762485</v>
+        <v>-6.590376850962639e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1109912964866739</v>
+        <v>0.02837624927600438</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2222790143693965</v>
+        <v>0.05682822725889063</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4288180764371204</v>
+        <v>0.1096324578251719</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.9692091466867835</v>
+        <v>0.2477894589676733</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1319073531543832</v>
+        <v>0.03372304958318231</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.8036612722103675</v>
+        <v>0.2054653340305118</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02676498316748519</v>
+        <v>0.006842188562069244</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.7250775289252778</v>
+        <v>0.1853737683277901</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02317966493616919</v>
+        <v>0.005924421589592836</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.7446422865812115</v>
+        <v>0.1903739574568235</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01133166228766422</v>
+        <v>0.002893773410395921</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.331760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.7440967471048301</v>
+        <v>0.1902309670682372</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.005405853706746107</v>
+        <v>0.001378115234991904</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.7435639760162698</v>
+        <v>0.1900910351897057</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002249119612111675</v>
+        <v>0.0005711950601470939</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.331760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.7426500378087603</v>
+        <v>0.1898536105433551</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001557634767302897</v>
+        <v>0.0003947258318335312</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.743513589525875</v>
+        <v>0.1900707882171653</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0006470184679483451</v>
+        <v>0.0001618703391290725</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.331760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.7432489379781341</v>
+        <v>0.1899993685347054</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003330948352202433</v>
+        <v>8.119413783282883e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.331760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.7432674535704525</v>
+        <v>0.1900003814333554</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001277906138719088</v>
+        <v>2.911616561926511e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.7431893986409644</v>
+        <v>0.1899766492426984</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>6.772442418965789e-05</v>
+        <v>1.332426436274844e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.7431963833253616</v>
+        <v>0.1899747168322629</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.057431912786162e-05</v>
+        <v>4.034747715012475e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.7431902906099691</v>
+        <v>0.189969433370553</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.205041969913093e-05</v>
+        <v>-7.373950752172664e-07</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.7431832104029619</v>
+        <v>0.1899638814344234</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>2.378749652309724e-06</v>
+        <v>-3.155312586922569e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.7431758963017496</v>
+        <v>0.1899582311692701</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.69277857293039e-06</v>
+        <v>-4.173194643232597e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7431701223228127</v>
+        <v>0.1899529898479693</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.728542685550439e-06</v>
+        <v>-4.68213567138761e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.7431643531799451</v>
+        <v>0.1899477019091188</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.634963333793937e-06</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.7431588095118427</v>
+        <v>0.1899424300750678</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.777674021158921e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.7431538883581212</v>
+        <v>0.1899424699305401</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.331760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.7431539282135935</v>
+        <v>0.1899425097860123</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.743153920242499</v>
+        <v>0.1899425018149179</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.7431540796643882</v>
+        <v>0.189942661236807</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.331760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.7431539840112548</v>
+        <v>0.1899425655836735</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.7431543347394111</v>
+        <v>0.1899429163118298</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.7431540876354826</v>
+        <v>0.1899426692079015</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.7431540477800104</v>
+        <v>0.1899426293524292</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.7431539840112548</v>
+        <v>0.1899425655836735</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.7431540557511048</v>
+        <v>0.1899426373235236</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.7431539840112548</v>
+        <v>0.1899425655836735</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.7431540876354826</v>
+        <v>0.1899426692079015</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.7431541832886164</v>
+        <v>0.1899427648610352</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.7431541195198604</v>
+        <v>0.1899427010922793</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.7431540796643882</v>
+        <v>0.189942661236807</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.7431540557511048</v>
+        <v>0.1899426373235236</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.7431538086471767</v>
+        <v>0.1899423902195955</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.331760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.7431537289362319</v>
+        <v>0.1899423105086507</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.7431537767627987</v>
+        <v>0.1899423583352175</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.7431538963292157</v>
+        <v>0.1899424779016345</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.7431538803870268</v>
+        <v>0.1899424619594456</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.7431538963292157</v>
+        <v>0.1899424779016345</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.7431538803870268</v>
+        <v>0.1899424619594456</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.7431539361846881</v>
+        <v>0.1899425177571068</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.7431539361846881</v>
+        <v>0.1899425177571068</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.331760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.7431539361846881</v>
+        <v>0.1899425177571068</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.7431540876354826</v>
+        <v>0.1899426692079015</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.331760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.7431543028550331</v>
+        <v>0.189942884427452</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.7431542151729942</v>
+        <v>0.189942796745413</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.331760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.7431541673464275</v>
+        <v>0.1899427489188462</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.331760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.7431542151729942</v>
+        <v>0.189942796745413</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.7431540318378215</v>
+        <v>0.1899426134102403</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.7431540398089159</v>
+        <v>0.1899426213813347</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.7431540477800104</v>
+        <v>0.1899426293524292</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.7431540557511048</v>
+        <v>0.1899426373235236</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.7431540557511048</v>
+        <v>0.1899426373235236</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.7431540956065771</v>
+        <v>0.1899426771789959</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.743154159375333</v>
+        <v>0.1899427409477518</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.7431542709706553</v>
+        <v>0.1899428525430742</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.7431543187972222</v>
+        <v>0.1899429003696409</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.331760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.7431542789417498</v>
+        <v>0.1899428605141686</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.7431542072018997</v>
+        <v>0.1899427887743185</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.7431543267683166</v>
+        <v>0.1899429083407354</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.7431541673464275</v>
+        <v>0.1899427489188462</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.7431539361846881</v>
+        <v>0.1899425177571068</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.7431538883581212</v>
+        <v>0.1899424699305401</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.743153920242499</v>
+        <v>0.1899425018149179</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.7431539840112548</v>
+        <v>0.1899425655836735</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.7431539840112548</v>
+        <v>0.1899425655836735</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.7431539043003101</v>
+        <v>0.189942485872729</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.7431537847338932</v>
+        <v>0.1899423663063119</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.7431537448784208</v>
+        <v>0.1899423264508396</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.7431538883581212</v>
+        <v>0.1899424699305401</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.743154023866727</v>
+        <v>0.1899426054391458</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.331760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.7431540079245381</v>
+        <v>0.1899425894969569</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.331760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.7431539840112548</v>
+        <v>0.1899425655836735</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.7431539441557825</v>
+        <v>0.1899425257282013</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.501156825476262</v>
+        <v>3.031863202161869</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.7431538405315545</v>
+        <v>0.1899424221039733</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.501156825476262</v>
+        <v>3.031863202161869</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.7431537209651374</v>
+        <v>0.1899423025375563</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.417459022789986</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.7431538405315545</v>
+        <v>0.1899424221039733</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.417459022789986</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.7431538883581212</v>
+        <v>0.1899424699305401</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.7431539840112548</v>
+        <v>0.1899425655836735</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.7431538644448379</v>
+        <v>0.1899424460172567</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.017459022789986</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.7431538724159323</v>
+        <v>0.1899424539883512</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_5_000001.xlsx
+++ b/out/Attention-MambaAMT_repeat_5_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.01612649947684261</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.01612649947684264</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-0.01612649947684264</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-0.6636503946122936</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.6636503946122936</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.01612649947684261</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-0.01612649947684261</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-0.6636503946122936</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.2161264994768427</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.9011568254762614</v>
+        <v>0.6313973956586084</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.931760215741336</v>
+        <v>0.6313973956586084</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002577772592762485</v>
+        <v>-0.0002044563129749149</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1109912964866739</v>
+        <v>0.08803284512498002</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2222790143693965</v>
+        <v>0.1763008416093416</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4288180764371204</v>
+        <v>0.3401182645523348</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.9692091466867835</v>
+        <v>0.7687294345096357</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1319073531543832</v>
+        <v>0.1046222847812487</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.8036612722103675</v>
+        <v>0.6374251784979875</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02676498316748519</v>
+        <v>0.02122863983053788</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.931760215741336</v>
+        <v>0.6313973956586082</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.7250775289252778</v>
+        <v>0.5750965017977078</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02317966493616919</v>
+        <v>0.018384587767112</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.501156825476262</v>
+        <v>0.6313973956586084</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.7446422865812115</v>
+        <v>0.5906142854419346</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01133166228766422</v>
+        <v>0.008987427730003862</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.2161264994768427</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.7440967471048301</v>
+        <v>0.5901812027207616</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.005405853706746107</v>
+        <v>0.004286666258141547</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.501156825476262</v>
+        <v>0.4313973956586084</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.7435639760162698</v>
+        <v>0.589757589840031</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002249119612111675</v>
+        <v>0.001783153172166634</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.2161264994768427</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.7426500378087603</v>
+        <v>0.5890316337821537</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001557634767302897</v>
+        <v>0.001234304412981952</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.501156825476262</v>
+        <v>0.4313973956586084</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.743513589525875</v>
+        <v>0.5897154703538506</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0006470184679483451</v>
+        <v>0.0005123624800024912</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.331760215741336</v>
+        <v>0.4313973956586084</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.7432489379781341</v>
+        <v>0.58950454369356</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003330948352202433</v>
+        <v>0.0002629368160539872</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.331760215741336</v>
+        <v>0.4313973956586084</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.7432674535704525</v>
+        <v>0.5895181845303471</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001277906138719088</v>
+        <v>0.0001004976813764967</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9011568254762614</v>
+        <v>0.6313973956586084</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.7431893986409644</v>
+        <v>0.5894552588330849</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>6.772442418965789e-05</v>
+        <v>5.226332613358888e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.931760215741336</v>
+        <v>0.6313973956586084</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.7431963833253616</v>
+        <v>0.5894597434190195</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.057431912786162e-05</v>
+        <v>2.323358660941399e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.7431902906099691</v>
+        <v>0.5894538745397518</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.205041969913093e-05</v>
+        <v>8.32064038994604e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.7431832104029619</v>
+        <v>0.5894472174936498</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>2.378749652309724e-06</v>
+        <v>9.952340925016508e-07</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.7431758963017496</v>
+        <v>0.5894403372864148</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.69277857293039e-06</v>
+        <v>-2.519583929697793e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.931760215741336</v>
+        <v>0.6313973956586084</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7431701223228127</v>
+        <v>0.5894347089756452</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.728542685550439e-06</v>
+        <v>-4.04640701416283e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768427</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.7431643531799451</v>
+        <v>0.589429036465361</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.7431588095118427</v>
+        <v>0.5894234927972586</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.7431538883581212</v>
+        <v>0.5894185716435372</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.2161264994768427</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.7431539282135935</v>
+        <v>0.5894186114990094</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768427</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.743153920242499</v>
+        <v>0.589418603527915</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768427</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.7431540796643882</v>
+        <v>0.5894187629498041</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.7431539840112548</v>
+        <v>0.5894186672966706</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.7431543347394111</v>
+        <v>0.5894190180248269</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.7431540876354826</v>
+        <v>0.5894187709208986</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.7431540477800104</v>
+        <v>0.5894187310654263</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.931760215741336</v>
+        <v>0.6313973956586084</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.7431539840112548</v>
+        <v>0.5894186672966706</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.931760215741336</v>
+        <v>0.6313973956586084</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.7431540557511048</v>
+        <v>0.5894187390365208</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9011568254762614</v>
+        <v>0.6313973956586084</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.7431539840112548</v>
+        <v>0.5894186672966706</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.01612649947684264</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.7431540876354826</v>
+        <v>0.5894187709208986</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.01612649947684264</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.7431541832886164</v>
+        <v>0.5894188665740322</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.7431541195198604</v>
+        <v>0.5894188028052764</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.7431540796643882</v>
+        <v>0.5894187629498041</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.7431540557511048</v>
+        <v>0.5894187390365208</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.7431538086471767</v>
+        <v>0.5894184919325925</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.331760215741336</v>
+        <v>0.4313973956586084</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.7431537289362319</v>
+        <v>0.5894184122216478</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.7431537767627987</v>
+        <v>0.5894184600482145</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.7431538963292157</v>
+        <v>0.5894185796146316</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.7431538803870268</v>
+        <v>0.5894185636724427</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.7431538963292157</v>
+        <v>0.5894185796146316</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.7431538803870268</v>
+        <v>0.5894185636724427</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.931760215741336</v>
+        <v>0.6313973956586084</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.7431539361846881</v>
+        <v>0.5894186194701039</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.501156825476262</v>
+        <v>0.6313973956586083</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.7431539361846881</v>
+        <v>0.5894186194701039</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.2161264994768427</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.7431539361846881</v>
+        <v>0.5894186194701039</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.501156825476262</v>
+        <v>0.4313973956586082</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.7431540876354826</v>
+        <v>0.5894187709208986</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.2161264994768427</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.7431543028550331</v>
+        <v>0.5894189861404491</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.501156825476262</v>
+        <v>0.4313973956586082</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.7431542151729942</v>
+        <v>0.58941889845841</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.331760215741336</v>
+        <v>0.4313973956586082</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.7431541673464275</v>
+        <v>0.5894188506318433</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.331760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.7431542151729942</v>
+        <v>0.58941889845841</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.7431540318378215</v>
+        <v>0.5894187151232373</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.7431540398089159</v>
+        <v>0.5894187230943319</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.7431540477800104</v>
+        <v>0.5894187310654263</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.7431540557511048</v>
+        <v>0.5894187390365208</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.931760215741336</v>
+        <v>0.6313973956586084</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.7431540557511048</v>
+        <v>0.5894187390365208</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768427</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.7431540956065771</v>
+        <v>0.589418778891993</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.743154159375333</v>
+        <v>0.5894188426607488</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.7431542709706553</v>
+        <v>0.5894189542560713</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768427</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.7431543187972222</v>
+        <v>0.589419002082638</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.2161264994768427</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.7431542789417498</v>
+        <v>0.5894189622271657</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768427</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.7431542072018997</v>
+        <v>0.5894188904873155</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.7431543267683166</v>
+        <v>0.5894190100537324</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.7431541673464275</v>
+        <v>0.5894188506318433</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768427</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.7431539361846881</v>
+        <v>0.5894186194701039</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.931760215741336</v>
+        <v>0.6313973956586084</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.7431538883581212</v>
+        <v>0.5894185716435372</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.743153920242499</v>
+        <v>0.589418603527915</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.7431539840112548</v>
+        <v>0.5894186672966706</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.7431539840112548</v>
+        <v>0.5894186672966706</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.7431539043003101</v>
+        <v>0.5894185875857261</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.7431537847338932</v>
+        <v>0.589418468019309</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.7431537448784208</v>
+        <v>0.5894184281638367</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.7431538883581212</v>
+        <v>0.5894185716435372</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.743154023866727</v>
+        <v>0.5894187071521428</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.331760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.7431540079245381</v>
+        <v>0.5894186912099539</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.331760215741336</v>
+        <v>0.4313973956586081</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.7431539840112548</v>
+        <v>0.5894186672966706</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768428</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.7431539441557825</v>
+        <v>0.5894186274411983</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.7431538405315545</v>
+        <v>0.5894185238169705</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.7431537209651374</v>
+        <v>0.5894184042505534</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768428</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.7431538405315545</v>
+        <v>0.5894185238169705</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.2161264994768428</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.7431538883581212</v>
+        <v>0.5894185716435372</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.501156825476262</v>
+        <v>0.4313973956586081</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.7431539840112548</v>
+        <v>0.5894186672966706</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.2161264994768427</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.7431538644448379</v>
+        <v>0.5894185477302538</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.501156825476262</v>
+        <v>0.3076354480908828</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.7431538724159323</v>
+        <v>0.5894185557013483</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_5_000001.xlsx
+++ b/out/Attention-MambaAMT_repeat_5_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.01281598955392838</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.006571389734745026</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.01765557378530502</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.01117166876792908</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.01538003236055374</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.005717270076274872</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.01148492842912674</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.005140520632266998</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.00995984673500061</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.003047823905944824</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.009464718401432037</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.004944346845149994</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.0104992464184761</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.01517584174871445</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.005190581083297729</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.01079104840755463</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.01851579546928406</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.16</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.01064886897802353</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.006180301308631897</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.01176188141107559</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.3</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.007070720195770264</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.01323841512203217</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.01107592135667801</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.01247691363096237</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.02123235166072845</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.01850344985723495</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.01468221098184586</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.01171048730611801</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.01706115901470184</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.01612649947684261</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.01272695139050484</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.01612649947684264</v>
+        <v>0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.01922673732042313</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.01612649947684264</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.004906490445137024</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.6636503946122936</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.0001375451683998108</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.6636503946122936</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.00161183625459671</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.2161264994768426</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.00147712230682373</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.01612649947684261</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.004924632608890533</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.01612649947684261</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.008665062487125397</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.6636503946122936</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.01126451045274734</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.2161264994768426</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.005209788680076599</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.2161264994768427</v>
+        <v>-0.16</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.0005757585167884827</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.6313973956586084</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.03348370641469955</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.6313973956586084</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.0401437059044838</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.278921290794059</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002044563129749149</v>
+        <v>-0.0001702408744366839</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.08803284512498002</v>
+        <v>0.07330077777373428</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.05519659817218781</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.278921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.1763008416093416</v>
+        <v>0.1467971759432526</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3401182645523348</v>
+        <v>0.2831996698953014</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.05652220547199249</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.278921290794059</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.7687294345096357</v>
+        <v>0.6400831868157596</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1046222847812487</v>
+        <v>0.08711329698371349</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.03872115537524223</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.278921290794059</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.6374251784979875</v>
+        <v>0.5307526231656382</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02122863983053788</v>
+        <v>0.01767614252776867</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.01486719399690628</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.6313973956586082</v>
+        <v>-0.16</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.5750965017977078</v>
+        <v>0.4788543111816319</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.018384587767112</v>
+        <v>0.01530832500785563</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.0102357342839241</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.6313973956586084</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.5906142854419346</v>
+        <v>0.4917752774562403</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.008987427730003862</v>
+        <v>0.00748238961545394</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.008456744253635406</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.2161264994768427</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.5901812027207616</v>
+        <v>0.4914138391048955</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.004286666258141547</v>
+        <v>0.003568381776201306</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.006003275513648987</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.4313973956586084</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.589757589840031</v>
+        <v>0.4910602829844139</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001783153172166634</v>
+        <v>0.001483643082930753</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.00077800452709198</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.2161264994768427</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.5890316337821537</v>
+        <v>0.4904549732263382</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001234304412981952</v>
+        <v>0.001026724782164925</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.009176447987556458</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.4313973956586084</v>
+        <v>-0.3</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.5897154703538506</v>
+        <v>0.4910236470363983</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0005123624800024912</v>
+        <v>0.0004260280188314653</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.01733608171343803</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.4313973956586084</v>
+        <v>-0.3</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.58950454369356</v>
+        <v>0.4908470842272644</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002629368160539872</v>
+        <v>0.0002181693181098049</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.02088885381817818</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.4313973956586084</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.5895181845303471</v>
+        <v>0.4908576145057606</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001004976813764967</v>
+        <v>8.265230243718883e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.0185384601354599</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.6313973956586084</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.5894552588330849</v>
+        <v>0.4908043437054495</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>5.226332613358888e-05</v>
+        <v>4.310119395221467e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.005396462976932526</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.6313973956586084</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.5894597434190195</v>
+        <v>0.4908072705833183</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.323358660941399e-05</v>
+        <v>1.871621275190775e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.008290372788906097</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.278921290794059</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.5894538745397518</v>
+        <v>0.4908015474204531</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>8.32064038994604e-06</v>
+        <v>6.189337927554673e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.01267298310995102</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.278921290794059</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.5894472174936498</v>
+        <v>0.4907951822846045</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>9.952340925016508e-07</v>
+        <v>-3.882814673064221e-07</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.0113920196890831</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.278921290794059</v>
+        <v>0.16</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.5894403372864148</v>
+        <v>0.4907886642314969</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-2.519583929697793e-06</v>
+        <v>-2.932986608081494e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.003235459327697754</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.6313973956586084</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5894347089756452</v>
+        <v>0.4907831326680945</v>
       </c>
     </row>
     <row r="61">
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.001022271811962128</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.2161264994768427</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.589429036465361</v>
+        <v>0.4907775558109437</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.634963333793937e-06</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.002501897513866425</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5894234927972586</v>
+        <v>0.4907721484682867</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.006374865770339966</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.2161264994768426</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5894185716435372</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.0002150833606719971</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.2161264994768427</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5894186114990094</v>
+        <v>0.4907672671700376</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.001022003591060638</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.2161264994768427</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.589418603527915</v>
+        <v>0.4907672591989432</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.01662812381982803</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.2161264994768427</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5894187629498041</v>
+        <v>0.4907674186208323</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.00373927503824234</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.2161264994768426</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5894186672966706</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.01079899817705154</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.2161264994768426</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5894190180248269</v>
+        <v>0.4907676736958551</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.0133187547326088</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5894187709208986</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.01155403256416321</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.2161264994768426</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5894187310654263</v>
+        <v>0.4907673867364544</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.00138140469789505</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.6313973956586084</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5894186672966706</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.002410963177680969</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.6313973956586084</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5894187390365208</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.03103332966566086</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.6313973956586084</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5894186672966706</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.0354342870414257</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.01612649947684264</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5894187709208986</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.01433387398719788</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.01612649947684264</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5894188665740322</v>
+        <v>0.4907675222450604</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.01450937986373901</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5894188028052764</v>
+        <v>0.4907674584763045</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.001874707639217377</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5894187629498041</v>
+        <v>0.4907674186208323</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.003076925873756409</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5894187390365208</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.004875697195529938</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.2161264994768426</v>
+        <v>0.3</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5894184919325925</v>
+        <v>0.4907671476036208</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.009290561079978943</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.4313973956586084</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5894184122216478</v>
+        <v>0.490767067892676</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.01842669770121574</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.278921290794059</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5894184600482145</v>
+        <v>0.4907671157192427</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.003605633974075317</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.278921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5894185796146316</v>
+        <v>0.4907672352856598</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.008929163217544556</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.278921290794059</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5894185636724427</v>
+        <v>0.4907672193434709</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.004731796681880951</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.278921290794059</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5894185796146316</v>
+        <v>0.4907672352856598</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.008020848035812378</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.278921290794059</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5894185636724427</v>
+        <v>0.4907672193434709</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.009141460061073303</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.6313973956586084</v>
+        <v>0.3</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5894186194701039</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.002775542438030243</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.6313973956586083</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5894186194701039</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.001804985105991364</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.2161264994768427</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5894186194701039</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.01335429400205612</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.4313973956586082</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5894187709208986</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.004505552351474762</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.2161264994768427</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5894189861404491</v>
+        <v>0.4907676418114773</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.007715485990047455</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.4313973956586082</v>
+        <v>-0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.58941889845841</v>
+        <v>0.4907675541294382</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.005679510533809662</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.4313973956586082</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5894188506318433</v>
+        <v>0.4907675063028715</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.003796473145484924</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.278921290794059</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.58941889845841</v>
+        <v>0.4907675541294382</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.002976782619953156</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.278921290794059</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5894187151232373</v>
+        <v>0.4907673707942655</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.004275552928447723</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.278921290794059</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5894187230943319</v>
+        <v>0.49076737876536</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.009743876755237579</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.278921290794059</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5894187310654263</v>
+        <v>0.4907673867364544</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.004619494080543518</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.278921290794059</v>
+        <v>0.3</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5894187390365208</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.0001161769032478333</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.6313973956586084</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5894187390365208</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.004619188606739044</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.2161264994768427</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.589418778891993</v>
+        <v>0.4907674345630212</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.01087431609630585</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5894188426607488</v>
+        <v>0.4907674983317771</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.003607586026191711</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5894189542560713</v>
+        <v>0.4907676099270994</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.001632310450077057</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.2161264994768427</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.589419002082638</v>
+        <v>0.4907676577536662</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.003452859818935394</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.2161264994768427</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5894189622271657</v>
+        <v>0.4907676178981939</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.003782071173191071</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.2161264994768427</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5894188904873155</v>
+        <v>0.4907675461583438</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.01113922894001007</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5894190100537324</v>
+        <v>0.4907676657247606</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.008691824972629547</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5894188506318433</v>
+        <v>0.4907675063028715</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.013954758644104</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.2161264994768427</v>
+        <v>0.16</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5894186194701039</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.008081629872322083</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.6313973956586084</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5894185716435372</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.002713344991207123</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.278921290794059</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.589418603527915</v>
+        <v>0.4907672591989432</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.009149752557277679</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.278921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5894186672966706</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.001456655561923981</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.278921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5894186672966706</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.004335470497608185</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.278921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5894185875857261</v>
+        <v>0.4907672432567542</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.0086522176861763</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.278921290794059</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.589418468019309</v>
+        <v>0.4907671236903371</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.007797740399837494</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.278921290794059</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5894184281638367</v>
+        <v>0.4907670838348649</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.007397562265396118</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.278921290794059</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5894185716435372</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.004510574042797089</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.278921290794059</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5894187071521428</v>
+        <v>0.4907673628231711</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.002128511667251587</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.278921290794059</v>
+        <v>-0.3</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5894186912099539</v>
+        <v>0.4907673468809822</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.004122301936149597</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.4313973956586081</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5894186672966706</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.001103602349758148</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.2161264994768428</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5894186274411983</v>
+        <v>0.4907672831122265</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.01225661486387253</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5894185238169705</v>
+        <v>0.4907671794879986</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.02076046913862228</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5894184042505534</v>
+        <v>0.4907670599215815</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.005132384598255157</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.2161264994768428</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5894185238169705</v>
+        <v>0.4907671794879986</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.002052940428256989</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.2161264994768428</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5894185716435372</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.001395158469676971</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.4313973956586081</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5894186672966706</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.000508531928062439</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.2161264994768427</v>
+        <v>0.09000000000000014</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5894185477302538</v>
+        <v>0.4907672034012819</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.0149260088801384</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.3076354480908828</v>
+        <v>0.1600000000000002</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5894185557013483</v>
+        <v>0.4907672113723764</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_5_000001.xlsx
+++ b/out/Attention-MambaAMT_repeat_5_000001.xlsx
@@ -39899,7 +39899,7 @@
         <v>0.008456744253635406</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC49" t="n">
         <v>0.4914138391048955</v>
@@ -40694,7 +40694,7 @@
         <v>-0.006003275513648987</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC50" t="n">
         <v>0.4910602829844139</v>
@@ -41489,7 +41489,7 @@
         <v>0.00077800452709198</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC51" t="n">
         <v>0.4904549732263382</v>
@@ -42284,7 +42284,7 @@
         <v>-0.009176447987556458</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC52" t="n">
         <v>0.4910236470363983</v>
@@ -43079,7 +43079,7 @@
         <v>0.01733608171343803</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC53" t="n">
         <v>0.4908470842272644</v>
@@ -43874,7 +43874,7 @@
         <v>0.02088885381817818</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.4399999999999999</v>
+        <v>-0.3</v>
       </c>
       <c r="JC54" t="n">
         <v>0.4908576145057606</v>
@@ -44669,7 +44669,7 @@
         <v>-0.0185384601354599</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC55" t="n">
         <v>0.4908043437054495</v>
@@ -45464,7 +45464,7 @@
         <v>0.005396462976932526</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC56" t="n">
         <v>0.4908072705833183</v>
@@ -46259,7 +46259,7 @@
         <v>0.008290372788906097</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC57" t="n">
         <v>0.4908015474204531</v>
@@ -47054,7 +47054,7 @@
         <v>0.01267298310995102</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC58" t="n">
         <v>0.4907951822846045</v>
